--- a/artfynd/A 16823-2024 artfynd.xlsx
+++ b/artfynd/A 16823-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117684195</v>
+        <v>117684194</v>
       </c>
       <c r="B3" t="n">
-        <v>97864</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,26 +819,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219864</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117684207</v>
+        <v>117684404</v>
       </c>
       <c r="B4" t="n">
-        <v>106765</v>
+        <v>57990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,24 +945,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
@@ -975,7 +984,7 @@
         <v>6318293</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,11 +1024,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1036,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117684193</v>
+        <v>117684205</v>
       </c>
       <c r="B5" t="n">
-        <v>97865</v>
+        <v>97864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,16 +1056,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219865</v>
+        <v>219864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,7 +1085,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1090,13 +1094,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694629</v>
+        <v>694422</v>
       </c>
       <c r="R5" t="n">
-        <v>6318197</v>
+        <v>6318293</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,11 +1132,6 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Många orkidéer på gång (blad).</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1144,7 +1143,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkfuktäng.</t>
+          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1162,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117684205</v>
+        <v>117684402</v>
       </c>
       <c r="B6" t="n">
-        <v>97864</v>
+        <v>57990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,40 +1173,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219864</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1216,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694422</v>
+        <v>694677</v>
       </c>
       <c r="R6" t="n">
-        <v>6318293</v>
+        <v>6318179</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,11 +1256,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1283,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117684404</v>
+        <v>117684193</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>97865</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,35 +1284,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>219865</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1332,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694422</v>
+        <v>694629</v>
       </c>
       <c r="R7" t="n">
-        <v>6318293</v>
+        <v>6318197</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,6 +1364,11 @@
           <t>2024-05-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många orkidéer på gång (blad).</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1378,6 +1377,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkfuktäng.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1394,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117684194</v>
+        <v>117684207</v>
       </c>
       <c r="B8" t="n">
-        <v>97838</v>
+        <v>106765</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,55 +1410,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694629</v>
+        <v>694422</v>
       </c>
       <c r="R8" t="n">
-        <v>6318197</v>
+        <v>6318293</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,11 +1476,6 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Många orkidéer på gång (blad).</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1502,7 +1487,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkfuktäng.</t>
+          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1520,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117684402</v>
+        <v>117684195</v>
       </c>
       <c r="B9" t="n">
-        <v>57990</v>
+        <v>97864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,35 +1517,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>219864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1569,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694677</v>
+        <v>694629</v>
       </c>
       <c r="R9" t="n">
-        <v>6318179</v>
+        <v>6318197</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1607,6 +1597,11 @@
           <t>2024-05-11</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många orkidéer på gång (blad).</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1615,6 +1610,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkfuktäng.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 16823-2024 artfynd.xlsx
+++ b/artfynd/A 16823-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117684194</v>
+        <v>117684402</v>
       </c>
       <c r="B3" t="n">
-        <v>97838</v>
+        <v>57991</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,40 +815,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694629</v>
+        <v>694677</v>
       </c>
       <c r="R3" t="n">
-        <v>6318197</v>
+        <v>6318179</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,11 +890,6 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Många orkidéer på gång (blad).</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -908,11 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkfuktäng.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117684404</v>
+        <v>117684207</v>
       </c>
       <c r="B4" t="n">
-        <v>57990</v>
+        <v>106767</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,33 +930,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>220079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
@@ -984,7 +960,7 @@
         <v>6318293</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,6 +1000,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1043,7 +1024,7 @@
         <v>117684205</v>
       </c>
       <c r="B5" t="n">
-        <v>97864</v>
+        <v>97866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1161,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117684402</v>
+        <v>117684195</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>97866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,35 +1154,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>219864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1210,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694677</v>
+        <v>694629</v>
       </c>
       <c r="R6" t="n">
-        <v>6318179</v>
+        <v>6318197</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,6 +1234,11 @@
           <t>2024-05-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Många orkidéer på gång (blad).</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1256,6 +1247,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkfuktäng.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1272,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117684193</v>
+        <v>117684194</v>
       </c>
       <c r="B7" t="n">
-        <v>97865</v>
+        <v>97840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,26 +1284,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219865</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1398,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117684207</v>
+        <v>117684404</v>
       </c>
       <c r="B8" t="n">
-        <v>106765</v>
+        <v>57991</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,24 +1410,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
@@ -1444,7 +1449,7 @@
         <v>6318293</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,11 +1489,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117684195</v>
+        <v>117684193</v>
       </c>
       <c r="B9" t="n">
-        <v>97864</v>
+        <v>97867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,16 +1521,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219864</v>
+        <v>219865</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">

--- a/artfynd/A 16823-2024 artfynd.xlsx
+++ b/artfynd/A 16823-2024 artfynd.xlsx
@@ -675,64 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66371532</v>
+        <v>117684402</v>
       </c>
       <c r="B2" t="n">
-        <v>96359</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222118</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjärges, Valkmyr, Gtl</t>
+          <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694667.6703849945</v>
+        <v>694677</v>
       </c>
       <c r="R2" t="n">
-        <v>6318105.562344664</v>
+        <v>6318179</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst på båda sidor om vägen.</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,64 +769,54 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Arvid Svanborg</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Arvid Svanborg</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117684205</v>
+        <v>117684404</v>
       </c>
       <c r="B3" t="n">
-        <v>97866</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219864</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -863,7 +831,7 @@
         <v>6318293</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,11 +871,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,47 +887,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117684402</v>
+        <v>117684194</v>
       </c>
       <c r="B4" t="n">
-        <v>57991</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694677</v>
+        <v>694629</v>
       </c>
       <c r="R4" t="n">
-        <v>6318179</v>
+        <v>6318197</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,6 +974,11 @@
           <t>2024-05-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Många orkidéer på gång (blad).</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,6 +987,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkfuktäng.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1035,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117684194</v>
+        <v>117684195</v>
       </c>
       <c r="B5" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,26 +1019,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1080,7 +1048,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1161,47 +1129,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117684404</v>
+        <v>117684205</v>
       </c>
       <c r="B6" t="n">
-        <v>57991</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>219864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1216,7 +1184,7 @@
         <v>6318293</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,6 +1224,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1272,53 +1245,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117684207</v>
+        <v>117684193</v>
       </c>
       <c r="B7" t="n">
-        <v>106768</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>219865</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694422</v>
+        <v>694629</v>
       </c>
       <c r="R7" t="n">
-        <v>6318293</v>
+        <v>6318197</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,6 +1332,11 @@
           <t>2024-05-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många orkidéer på gång (blad).</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1361,7 +1348,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
+          <t>Kalkfuktäng.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1379,67 +1366,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117684195</v>
+        <v>117684207</v>
       </c>
       <c r="B8" t="n">
-        <v>97866</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>694629</v>
+        <v>694422</v>
       </c>
       <c r="R8" t="n">
-        <v>6318197</v>
+        <v>6318293</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,11 +1439,6 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Många orkidéer på gång (blad).</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1487,7 +1450,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkfuktäng.</t>
+          <t>Alvarmark, vinterfuktigt; åtminstone tidigare betat.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1505,15 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117684193</v>
+        <v>66371532</v>
       </c>
       <c r="B9" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,16 +1479,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219865</v>
+        <v>222118</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1540,32 +1498,29 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vamlingbo Bjärges 1:7 (2), Gtl</t>
+          <t>Bjärges, Valkmyr, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>694629</v>
+        <v>694668</v>
       </c>
       <c r="R9" t="n">
-        <v>6318197</v>
+        <v>6318106</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,17 +1544,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2017-06-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2017-06-23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Många orkidéer på gång (blad).</t>
+          <t>Minst på båda sidor om vägen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,21 +1565,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkfuktäng.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arvid Svanborg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arvid Svanborg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 16823-2024 artfynd.xlsx
+++ b/artfynd/A 16823-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684402</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684404</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684194</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684205</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684193</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684207</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,8 +1618,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66371532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>